--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484820_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484820_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. VALERO CHICA</t>
+          <t>F. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.5756</v>
+        <v>10.0007</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2514</v>
+        <v>6.8597</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3242</v>
+        <v>3.141</v>
       </c>
       <c r="G2" t="n">
-        <v>1.95</v>
+        <v>5.3535</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4883</v>
+        <v>0.5478</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4616</v>
+        <v>4.8057</v>
       </c>
       <c r="J2" t="n">
-        <v>1.0039</v>
+        <v>4.9928</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7982</v>
+        <v>1.1833</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2057</v>
+        <v>3.8095</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.3607</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3099</v>
+        <v>-0.6354</v>
       </c>
       <c r="O2" t="n">
-        <v>1.256</v>
+        <v>0.9962</v>
       </c>
       <c r="P2" t="n">
-        <v>1.887</v>
+        <v>1.1322</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R2" t="n">
-        <v>1.887</v>
+        <v>2.0757</v>
       </c>
       <c r="S2" t="n">
-        <v>4.8332</v>
+        <v>1.3263</v>
       </c>
       <c r="T2" t="n">
-        <v>3.9837</v>
+        <v>1.2634</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8495</v>
+        <v>0.063</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9054</v>
+        <v>2.1886</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2639</v>
+        <v>1.547</v>
       </c>
       <c r="X2" t="n">
         <v>0.6415999999999999</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F. GOMEZ CARBONELL</t>
+          <t>J. VALERO CHICA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.293900000000001</v>
+        <v>7.4174</v>
       </c>
       <c r="E3" t="n">
-        <v>6.391</v>
+        <v>3.2255</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9029</v>
+        <v>4.1919</v>
       </c>
       <c r="G3" t="n">
-        <v>5.3535</v>
+        <v>1.95</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5478</v>
+        <v>0.4883</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8057</v>
+        <v>1.4616</v>
       </c>
       <c r="J3" t="n">
-        <v>4.9928</v>
+        <v>1.0039</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1833</v>
+        <v>0.7982</v>
       </c>
       <c r="L3" t="n">
-        <v>3.8095</v>
+        <v>0.2057</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3607</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6354</v>
+        <v>-0.3099</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9962</v>
+        <v>1.256</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1322</v>
+        <v>1.887</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0757</v>
+        <v>1.887</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6196</v>
+        <v>2.675</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7947</v>
+        <v>1.9577</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1751</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1886</v>
+        <v>0.9054</v>
       </c>
       <c r="W3" t="n">
-        <v>1.547</v>
+        <v>0.2639</v>
       </c>
       <c r="X3" t="n">
         <v>0.6415999999999999</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>7.927</v>
+        <v>6.416</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9767</v>
+        <v>3.4711</v>
       </c>
       <c r="F4" t="n">
-        <v>3.9502</v>
+        <v>2.9449</v>
       </c>
       <c r="G4" t="n">
         <v>2.358</v>
@@ -766,13 +766,13 @@
         <v>2.0757</v>
       </c>
       <c r="S4" t="n">
-        <v>4.2302</v>
+        <v>2.7193</v>
       </c>
       <c r="T4" t="n">
-        <v>2.035</v>
+        <v>1.5294</v>
       </c>
       <c r="U4" t="n">
-        <v>2.1952</v>
+        <v>1.1899</v>
       </c>
       <c r="V4" t="n">
         <v>3.0371</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>6.0732</v>
+        <v>5.4256</v>
       </c>
       <c r="E5" t="n">
-        <v>7.7488</v>
+        <v>7.0483</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6756</v>
+        <v>-1.6227</v>
       </c>
       <c r="G5" t="n">
         <v>3.1984</v>
@@ -844,13 +844,13 @@
         <v>0.7548</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5354</v>
+        <v>0.8878</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5618</v>
+        <v>0.8613</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0264</v>
+        <v>0.0265</v>
       </c>
       <c r="V5" t="n">
         <v>1.528</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0891</v>
+        <v>2.7879</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3686</v>
+        <v>3.8558</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2795</v>
+        <v>-1.0679</v>
       </c>
       <c r="G6" t="n">
         <v>0.3176</v>
@@ -922,13 +922,13 @@
         <v>1.5096</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3415</v>
+        <v>0.3573</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1517</v>
+        <v>0.3355</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1899</v>
+        <v>0.0218</v>
       </c>
       <c r="V6" t="n">
         <v>1.547</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5853</v>
+        <v>0.539</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3306</v>
+        <v>2.4813</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.9159</v>
+        <v>-1.9423</v>
       </c>
       <c r="G8" t="n">
         <v>0.4884</v>
@@ -1078,13 +1078,13 @@
         <v>1.5096</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0546</v>
+        <v>1.0696</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3281</v>
+        <v>0.8227</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2734</v>
+        <v>0.2469</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6415999999999999</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3339</v>
+        <v>-2.0919</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9502</v>
+        <v>1.4832</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.2841</v>
+        <v>-3.5751</v>
       </c>
       <c r="G9" t="n">
         <v>-3.1255</v>
@@ -1156,13 +1156,13 @@
         <v>0.9435</v>
       </c>
       <c r="S9" t="n">
-        <v>1.8106</v>
+        <v>1.0525</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0886</v>
+        <v>0.6216</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7219</v>
+        <v>0.4309</v>
       </c>
       <c r="V9" t="n">
         <v>-0.019</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0885</v>
+        <v>-2.3515</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3947</v>
+        <v>-1.7899</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6939</v>
+        <v>-0.5616</v>
       </c>
       <c r="G10" t="n">
         <v>-2.3878</v>
@@ -1234,13 +1234,13 @@
         <v>0.3774</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1346</v>
+        <v>0.6024</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2228</v>
+        <v>0.3819</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0882</v>
+        <v>0.2205</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8764</v>
+        <v>-2.5766</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.303</v>
+        <v>-1.3471</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5734</v>
+        <v>-1.2295</v>
       </c>
       <c r="G11" t="n">
         <v>-0.9982</v>
@@ -1312,13 +1312,13 @@
         <v>0.9435</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6896</v>
+        <v>0.6102</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.622</v>
+        <v>0.3338</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.06759999999999999</v>
+        <v>0.2763</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1886</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.1278</v>
+        <v>-3.1498</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.64</v>
+        <v>-5.1382</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5122</v>
+        <v>1.9884</v>
       </c>
       <c r="G12" t="n">
         <v>-3.994</v>
@@ -1390,13 +1390,13 @@
         <v>2.0757</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7189</v>
+        <v>1.259</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6097</v>
+        <v>0.8921</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1093</v>
+        <v>0.3669</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6036</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>22.4978</v>
+        <v>23.9677</v>
       </c>
       <c r="E13" t="n">
-        <v>20.2305</v>
+        <v>21.7006</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2671</v>
+        <v>2.267100000000001</v>
       </c>
       <c r="G13" t="n">
         <v>4.7113</v>
@@ -1468,13 +1468,13 @@
         <v>14.1525</v>
       </c>
       <c r="S13" t="n">
-        <v>11.0898</v>
+        <v>12.5594</v>
       </c>
       <c r="T13" t="n">
-        <v>7.529500000000001</v>
+        <v>8.9994</v>
       </c>
       <c r="U13" t="n">
-        <v>3.559899999999999</v>
+        <v>3.5599</v>
       </c>
       <c r="V13" t="n">
         <v>5.7533</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9583</v>
+        <v>0.826</v>
       </c>
       <c r="E14" t="n">
         <v>1.423</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4647</v>
+        <v>-0.597</v>
       </c>
       <c r="G14" t="n">
         <v>1.8545</v>
@@ -1546,13 +1546,13 @@
         <v>1.1322</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8212</v>
+        <v>-0.9535</v>
       </c>
       <c r="T14" t="n">
         <v>-0.3992</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.422</v>
+        <v>-0.5543</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2072</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2039</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8378</v>
+        <v>3.0327</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.6339</v>
+        <v>-2.504</v>
       </c>
       <c r="G16" t="n">
         <v>-0.6096</v>
@@ -1702,13 +1702,13 @@
         <v>0.9435</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0734</v>
+        <v>-0.7486</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3868</v>
+        <v>-0.192</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6866</v>
+        <v>-0.5567</v>
       </c>
       <c r="V16" t="n">
         <v>0.9434</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. BLEDA MIRANDA</t>
+          <t>S. VAL GUTIERREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0266</v>
+        <v>0.2751</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6626</v>
+        <v>2.6199</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.636</v>
+        <v>-2.3449</v>
       </c>
       <c r="G17" t="n">
-        <v>3.2138</v>
+        <v>-0.7945</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8931</v>
+        <v>0.9288999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3207</v>
+        <v>-1.7235</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2369</v>
+        <v>1.7033</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4143</v>
+        <v>3.0591</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8226</v>
+        <v>-1.3558</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0231</v>
+        <v>-2.4978</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5212</v>
+        <v>-2.1302</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4981</v>
+        <v>-0.3676</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5661</v>
+        <v>0.3774</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.887</v>
+        <v>-1.1322</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3209</v>
+        <v>1.5096</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1117</v>
+        <v>-1.1756</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2751</v>
+        <v>-0.4226</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3868</v>
+        <v>-0.753</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.5094</v>
+        <v>1.8678</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.9624</v>
+        <v>2.4714</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.547</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. VAL GUTIERREZ</t>
+          <t>C. BLEDA MIRANDA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6715</v>
+        <v>-0.2151</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3276</v>
+        <v>0.3703</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.9991</v>
+        <v>-0.5854</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7945</v>
+        <v>3.2138</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9288999999999999</v>
+        <v>1.8931</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.7235</v>
+        <v>1.3207</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7033</v>
+        <v>3.2369</v>
       </c>
       <c r="K18" t="n">
-        <v>3.0591</v>
+        <v>2.4143</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3558</v>
+        <v>0.8226</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.4978</v>
+        <v>-0.0231</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.1302</v>
+        <v>-0.5212</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3676</v>
+        <v>0.4981</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3774</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1322</v>
+        <v>-1.887</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5096</v>
+        <v>1.3209</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.1221</v>
+        <v>-0.3534</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7149</v>
+        <v>-0.0172</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.4073</v>
+        <v>-0.3362</v>
       </c>
       <c r="V18" t="n">
-        <v>1.8678</v>
+        <v>-2.5094</v>
       </c>
       <c r="W18" t="n">
-        <v>2.4714</v>
+        <v>-0.9624</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6036</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7427</v>
+        <v>-0.7161999999999999</v>
       </c>
       <c r="E19" t="n">
         <v>0.0035</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7462</v>
+        <v>-0.7197</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5004999999999999</v>
@@ -1936,13 +1936,13 @@
         <v>0.1887</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4309</v>
+        <v>-0.4044</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0588</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3721</v>
+        <v>-0.3456</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3576</v>
+        <v>-1.7989</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3732</v>
+        <v>0.886</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.7307</v>
+        <v>-2.6849</v>
       </c>
       <c r="G20" t="n">
         <v>-1.5205</v>
@@ -2014,13 +2014,13 @@
         <v>1.3209</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.08989999999999999</v>
+        <v>-0.5313</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3832</v>
+        <v>-0.104</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4731</v>
+        <v>-0.4273</v>
       </c>
       <c r="V20" t="n">
         <v>0.06419999999999999</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4476</v>
+        <v>-2.0676</v>
       </c>
       <c r="E21" t="n">
-        <v>1.947</v>
+        <v>1.7521</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.3946</v>
+        <v>-3.8197</v>
       </c>
       <c r="G21" t="n">
         <v>0.7008</v>
@@ -2092,13 +2092,13 @@
         <v>1.887</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7977</v>
+        <v>-1.4176</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3839</v>
+        <v>-0.5788</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.4137</v>
+        <v>-0.8388</v>
       </c>
       <c r="V21" t="n">
         <v>-1.1621</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0285</v>
+        <v>-2.6689</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6282</v>
+        <v>-1.5307</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4003</v>
+        <v>-1.1382</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2632</v>
@@ -2170,13 +2170,13 @@
         <v>0.1887</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1616</v>
+        <v>-0.802</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5879</v>
+        <v>-0.4904</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5737</v>
+        <v>-0.3115</v>
       </c>
       <c r="V22" t="n">
         <v>0.3398</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. MASSAMBA JOHANSSON</t>
+          <t>K. FEDOROV</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0048</v>
+        <v>-3.4681</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.864</v>
+        <v>-2.1871</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1407</v>
+        <v>-1.281</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7703</v>
+        <v>-0.6057</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.0276</v>
+        <v>0.0243</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2573</v>
+        <v>-0.63</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6495</v>
+        <v>-0.7454</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.0838</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7333</v>
+        <v>-1.258</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4198</v>
+        <v>0.1397</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9438</v>
+        <v>-0.4883</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.476</v>
+        <v>0.628</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.887</v>
+        <v>0.1887</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.774</v>
+        <v>-0.9435</v>
       </c>
       <c r="R23" t="n">
-        <v>1.887</v>
+        <v>1.1322</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1098</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7396</v>
+        <v>-0.4982</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3703</v>
+        <v>-0.1646</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2377</v>
+        <v>-2.3883</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2377</v>
+        <v>-2.3883</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>K. FEDOROV</t>
+          <t>S. MASSAMBA JOHANSSON</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.2379</v>
+        <v>-3.5909</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.382</v>
+        <v>-3.4743</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8559</v>
+        <v>-0.1166</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6057</v>
+        <v>-0.7703</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0243</v>
+        <v>-1.0276</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.63</v>
+        <v>0.2573</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7454</v>
+        <v>0.6495</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5125999999999999</v>
+        <v>-0.0838</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.258</v>
+        <v>0.7333</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1397</v>
+        <v>-1.4198</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4883</v>
+        <v>-0.9438</v>
       </c>
       <c r="O24" t="n">
-        <v>0.628</v>
+        <v>-0.476</v>
       </c>
       <c r="P24" t="n">
-        <v>0.1887</v>
+        <v>-1.887</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9435</v>
+        <v>-3.774</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1322</v>
+        <v>1.887</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4326</v>
+        <v>-0.696</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6931</v>
+        <v>-0.3498</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7395</v>
+        <v>-0.3462</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.3883</v>
+        <v>-0.2377</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.3883</v>
+        <v>-0.2377</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.83</v>
+        <v>-7.6375</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.6015</v>
+        <v>-5.7963</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.2285</v>
+        <v>-1.8412</v>
       </c>
       <c r="G25" t="n">
         <v>-5.0499</v>
@@ -2404,13 +2404,13 @@
         <v>1.6983</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9388</v>
+        <v>-0.7463</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.254</v>
+        <v>-0.4489</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6848</v>
+        <v>-0.2974</v>
       </c>
       <c r="V25" t="n">
         <v>-1.4639</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-22.4979</v>
+        <v>-19.8995</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.267100000000001</v>
+        <v>-2.266999999999998</v>
       </c>
       <c r="F26" t="n">
-        <v>-20.2306</v>
+        <v>-17.6326</v>
       </c>
       <c r="G26" t="n">
         <v>-4.7112</v>
@@ -2473,7 +2473,7 @@
         <v>-1.4041</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.9434999999999998</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q26" t="n">
         <v>-14.1525</v>
@@ -2482,19 +2482,19 @@
         <v>13.209</v>
       </c>
       <c r="S26" t="n">
-        <v>-11.0897</v>
+        <v>-8.4915</v>
       </c>
       <c r="T26" t="n">
         <v>-3.5599</v>
       </c>
       <c r="U26" t="n">
-        <v>-7.5299</v>
+        <v>-4.931599999999999</v>
       </c>
       <c r="V26" t="n">
         <v>-5.7534</v>
       </c>
       <c r="W26" t="n">
-        <v>4.603</v>
+        <v>4.603000000000001</v>
       </c>
       <c r="X26" t="n">
         <v>-10.3565</v>
